--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -16840,6 +16840,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B717" t="n">
+        <v>0</v>
+      </c>
+      <c r="C717" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D717" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E717" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F717" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G717" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.73717164993286</v>
+        <v>7.73717212677002</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>7.69620943069458</v>
+        <v>7.69621086120605</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91922235488892</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91011953353882</v>
+        <v>7.91012001037598</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>7.91011953353882</v>
+        <v>7.91012001037598</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G9" t="n">
-        <v>7.88281202316284</v>
+        <v>7.88281297683716</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640169143677</v>
+        <v>7.84640216827393</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G11" t="n">
-        <v>7.90101766586304</v>
+        <v>7.90101718902588</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G13" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G14" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G15" t="n">
-        <v>7.7553768157959</v>
+        <v>7.75537729263306</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G16" t="n">
-        <v>7.7553768157959</v>
+        <v>7.75537729263306</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>7.66435050964355</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>7.66435050964355</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G26" t="n">
-        <v>7.60973596572876</v>
+        <v>7.6097354888916</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.25</v>
       </c>
       <c r="G50" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>7.91922235488892</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>7.82819700241089</v>
+        <v>7.82819747924805</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G78" t="n">
-        <v>7.82819700241089</v>
+        <v>7.82819747924805</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82819700241089</v>
+        <v>7.82819747924805</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G91" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.25</v>
       </c>
       <c r="G97" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G98" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.25</v>
       </c>
       <c r="G114" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>7.23653078079224</v>
+        <v>7.23653125762939</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G128" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.5</v>
       </c>
       <c r="G140" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>6.84738731384277</v>
+        <v>6.84738779067993</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>6.84738731384277</v>
+        <v>6.84738779067993</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.25</v>
       </c>
       <c r="G183" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.25</v>
       </c>
       <c r="G184" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G187" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>8.25</v>
       </c>
       <c r="G194" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>7.96532821655273</v>
+        <v>7.96532869338989</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G212" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G215" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G223" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G224" t="n">
-        <v>7.96532821655273</v>
+        <v>7.96532869338989</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G236" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G247" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.25</v>
       </c>
       <c r="G249" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G250" t="n">
-        <v>8.24481391906738</v>
+        <v>8.2448148727417</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="n">
-        <v>8.38455581665039</v>
+        <v>8.38455677032471</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G281" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G282" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G283" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G284" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G285" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G287" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G288" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G290" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G291" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G292" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G293" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G294" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G295" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G297" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G298" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G302" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G303" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G309" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G311" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.5</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7</v>
       </c>
       <c r="G376" t="n">
-        <v>6.52132177352905</v>
+        <v>6.52132129669189</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7</v>
       </c>
       <c r="G380" t="n">
-        <v>6.52132177352905</v>
+        <v>6.52132129669189</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -19066,6 +19066,32 @@
         <v>6.80000019073486</v>
       </c>
       <c r="H719" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B720" t="n">
+        <v>400</v>
+      </c>
+      <c r="C720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="H720" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -16909,6 +16909,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B720" t="n">
+        <v>400</v>
+      </c>
+      <c r="C720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B721" t="n">
+        <v>0</v>
+      </c>
+      <c r="C721" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D721" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E721" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F721" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -16955,6 +16955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="722">
+      <c r="A722" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B722" t="n">
+        <v>0</v>
+      </c>
+      <c r="C722" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D722" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E722" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F722" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -16978,6 +16978,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B723" t="n">
+        <v>0</v>
+      </c>
+      <c r="C723" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D723" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E723" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F723" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G723" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17001,6 +17001,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B724" t="n">
+        <v>0</v>
+      </c>
+      <c r="C724" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D724" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E724" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F724" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G724" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17024,6 +17024,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="725">
+      <c r="A725" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B725" t="n">
+        <v>0</v>
+      </c>
+      <c r="C725" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D725" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E725" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F725" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G725" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17047,6 +17047,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B726" t="n">
+        <v>0</v>
+      </c>
+      <c r="C726" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D726" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E726" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F726" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G726" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B727" t="n">
+        <v>800</v>
+      </c>
+      <c r="C727" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="D727" t="n">
+        <v>7</v>
+      </c>
+      <c r="E727" t="n">
+        <v>7</v>
+      </c>
+      <c r="F727"/>
+      <c r="G727" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17086,7 +17086,9 @@
       <c r="E727" t="n">
         <v>7</v>
       </c>
-      <c r="F727"/>
+      <c r="F727" t="n">
+        <v>7.09999990463257</v>
+      </c>
       <c r="G727" t="s">
         <v>7</v>
       </c>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17093,6 +17093,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B728" t="n">
+        <v>0</v>
+      </c>
+      <c r="C728" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="D728" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="E728" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="F728" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="G728" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17116,6 +17116,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C729" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="D729" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="E729" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="F729" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="G729" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B730" t="n">
+        <v>600</v>
+      </c>
+      <c r="C730" t="n">
+        <v>7</v>
+      </c>
+      <c r="D730" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E730" t="n">
+        <v>7</v>
+      </c>
+      <c r="F730"/>
+      <c r="G730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17185,6 +17185,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B732" t="n">
+        <v>0</v>
+      </c>
+      <c r="C732" t="n">
+        <v>7</v>
+      </c>
+      <c r="D732" t="n">
+        <v>7</v>
+      </c>
+      <c r="E732" t="n">
+        <v>7</v>
+      </c>
+      <c r="F732" t="n">
+        <v>7</v>
+      </c>
+      <c r="G732" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17208,6 +17208,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B733" t="n">
+        <v>0</v>
+      </c>
+      <c r="C733" t="n">
+        <v>7</v>
+      </c>
+      <c r="D733" t="n">
+        <v>7</v>
+      </c>
+      <c r="E733" t="n">
+        <v>7</v>
+      </c>
+      <c r="F733" t="n">
+        <v>7</v>
+      </c>
+      <c r="G733" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17231,6 +17231,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B734" t="n">
+        <v>0</v>
+      </c>
+      <c r="C734" t="n">
+        <v>7</v>
+      </c>
+      <c r="D734" t="n">
+        <v>7</v>
+      </c>
+      <c r="E734" t="n">
+        <v>7</v>
+      </c>
+      <c r="F734" t="n">
+        <v>7</v>
+      </c>
+      <c r="G734" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17254,6 +17254,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B735" t="n">
+        <v>0</v>
+      </c>
+      <c r="C735" t="n">
+        <v>7</v>
+      </c>
+      <c r="D735" t="n">
+        <v>7</v>
+      </c>
+      <c r="E735" t="n">
+        <v>7</v>
+      </c>
+      <c r="F735" t="n">
+        <v>7</v>
+      </c>
+      <c r="G735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B736" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C736" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D736" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E736" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F736"/>
+      <c r="G736" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17300,6 +17300,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B737" t="n">
+        <v>0</v>
+      </c>
+      <c r="C737" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D737" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E737" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F737" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G737" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17323,6 +17323,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B738" t="n">
+        <v>0</v>
+      </c>
+      <c r="C738" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D738" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E738" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F738" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G738" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17346,6 +17346,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B739" t="n">
+        <v>0</v>
+      </c>
+      <c r="C739" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D739" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E739" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F739" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G739" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -17369,6 +17369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B740" t="n">
+        <v>0</v>
+      </c>
+      <c r="C740" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D740" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E740" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F740" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -21867,6 +21867,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" t="s">
+        <v>9</v>
+      </c>
+      <c r="B742" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C742" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D742" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E742" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F742" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G742" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="H742" t="n">
+        <v>0</v>
+      </c>
+      <c r="I742" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.73717164993286</v>
+        <v>7.7371711730957</v>
       </c>
       <c r="H2" t="n">
         <v>18200</v>
@@ -456,7 +456,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>7.69620943069458</v>
+        <v>7.69620990753174</v>
       </c>
       <c r="H3" t="n">
         <v>3600</v>
@@ -485,7 +485,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>7.69165849685669</v>
+        <v>7.69165802001953</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -514,7 +514,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G5" t="n">
-        <v>7.86460828781128</v>
+        <v>7.86460733413696</v>
       </c>
       <c r="H5" t="n">
         <v>1000</v>
@@ -543,7 +543,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91922283172607</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H6" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91012048721313</v>
+        <v>7.91011953353882</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>7.91012048721313</v>
+        <v>7.91011953353882</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640169143677</v>
+        <v>7.84640264511108</v>
       </c>
       <c r="H10" t="n">
         <v>5000</v>
@@ -688,7 +688,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G11" t="n">
-        <v>7.90101718902588</v>
+        <v>7.9010181427002</v>
       </c>
       <c r="H11" t="n">
         <v>3600</v>
@@ -717,7 +717,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>7.80999183654785</v>
+        <v>7.80999279022217</v>
       </c>
       <c r="H12" t="n">
         <v>2600</v>
@@ -746,7 +746,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G13" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H13" t="n">
         <v>200</v>
@@ -775,7 +775,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G14" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H14" t="n">
         <v>1400</v>
@@ -804,7 +804,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G15" t="n">
-        <v>7.75537729263306</v>
+        <v>7.7553768157959</v>
       </c>
       <c r="H15" t="n">
         <v>1000</v>
@@ -833,7 +833,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G16" t="n">
-        <v>7.75537729263306</v>
+        <v>7.7553768157959</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H18" t="n">
         <v>1600</v>
@@ -920,7 +920,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>7.66435098648071</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -978,7 +978,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G23" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>7.66435098648071</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H25" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G26" t="n">
-        <v>7.60973596572876</v>
+        <v>7.6097354888916</v>
       </c>
       <c r="H26" t="n">
         <v>1600</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H27" t="n">
         <v>1800</v>
@@ -1181,7 +1181,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H28" t="n">
         <v>1600</v>
@@ -1210,7 +1210,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H29" t="n">
         <v>400</v>
@@ -1239,7 +1239,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G32" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H34" t="n">
         <v>1200</v>
@@ -1384,7 +1384,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H36" t="n">
         <v>1200</v>
@@ -1442,7 +1442,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H38" t="n">
         <v>15400</v>
@@ -1500,7 +1500,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>7.69165849685669</v>
+        <v>7.69165802001953</v>
       </c>
       <c r="H39" t="n">
         <v>7600</v>
@@ -1529,7 +1529,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H40" t="n">
         <v>3400</v>
@@ -1558,7 +1558,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H44" t="n">
         <v>200</v>
@@ -1674,7 +1674,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H54" t="n">
         <v>1800</v>
@@ -1964,7 +1964,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H69" t="n">
         <v>800</v>
@@ -2399,7 +2399,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H71" t="n">
         <v>600</v>
@@ -2457,7 +2457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>7.91922283172607</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -3037,7 +3037,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3066,7 +3066,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H107" t="n">
         <v>200</v>
@@ -3501,7 +3501,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -21893,6 +21893,35 @@
         <v>0</v>
       </c>
       <c r="I742" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="s">
+        <v>9</v>
+      </c>
+      <c r="B743" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C743" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D743" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E743" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F743" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G743" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="H743" t="n">
+        <v>0</v>
+      </c>
+      <c r="I743" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -21925,6 +21925,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="s">
+        <v>9</v>
+      </c>
+      <c r="B744" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C744" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D744" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="E744" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F744" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G744" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="H744" t="n">
+        <v>0</v>
+      </c>
+      <c r="I744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B745" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C745" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D745" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E745" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F745" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G745" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H745" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I745" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.7371711730957</v>
+        <v>7.73717164993286</v>
       </c>
       <c r="H2" t="n">
         <v>18200</v>
@@ -456,7 +456,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>7.69620990753174</v>
+        <v>7.69620943069458</v>
       </c>
       <c r="H3" t="n">
         <v>3600</v>
@@ -485,7 +485,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>7.69165802001953</v>
+        <v>7.69165849685669</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -543,7 +543,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91922187805176</v>
+        <v>7.91922235488892</v>
       </c>
       <c r="H6" t="n">
         <v>1400</v>
@@ -659,7 +659,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640264511108</v>
+        <v>7.84640169143677</v>
       </c>
       <c r="H10" t="n">
         <v>5000</v>
@@ -688,7 +688,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G11" t="n">
-        <v>7.9010181427002</v>
+        <v>7.90101766586304</v>
       </c>
       <c r="H11" t="n">
         <v>3600</v>
@@ -717,7 +717,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>7.80999279022217</v>
+        <v>7.80999183654785</v>
       </c>
       <c r="H12" t="n">
         <v>2600</v>
@@ -746,7 +746,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G13" t="n">
-        <v>7.79178667068481</v>
+        <v>7.79178762435913</v>
       </c>
       <c r="H13" t="n">
         <v>200</v>
@@ -775,7 +775,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G14" t="n">
-        <v>7.79178667068481</v>
+        <v>7.79178762435913</v>
       </c>
       <c r="H14" t="n">
         <v>1400</v>
@@ -891,7 +891,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H18" t="n">
         <v>1600</v>
@@ -920,7 +920,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>7.66435146331787</v>
+        <v>7.66435050964355</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -978,7 +978,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G23" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>7.66435146331787</v>
+        <v>7.66435050964355</v>
       </c>
       <c r="H25" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G26" t="n">
-        <v>7.6097354888916</v>
+        <v>7.60973596572876</v>
       </c>
       <c r="H26" t="n">
         <v>1600</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H27" t="n">
         <v>1800</v>
@@ -1181,7 +1181,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H28" t="n">
         <v>1600</v>
@@ -1210,7 +1210,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H29" t="n">
         <v>400</v>
@@ -1239,7 +1239,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G32" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H34" t="n">
         <v>1200</v>
@@ -1384,7 +1384,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H36" t="n">
         <v>1200</v>
@@ -1442,7 +1442,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H38" t="n">
         <v>15400</v>
@@ -1500,7 +1500,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>7.69165802001953</v>
+        <v>7.69165849685669</v>
       </c>
       <c r="H39" t="n">
         <v>7600</v>
@@ -1529,7 +1529,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H40" t="n">
         <v>3400</v>
@@ -1558,7 +1558,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -2051,7 +2051,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268384933472</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H69" t="n">
         <v>800</v>
@@ -2399,7 +2399,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H71" t="n">
         <v>600</v>
@@ -2457,7 +2457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>7.91922187805176</v>
+        <v>7.91922235488892</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>7.82819747924805</v>
+        <v>7.82819700241089</v>
       </c>
       <c r="H77" t="n">
         <v>400</v>
@@ -2631,7 +2631,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G78" t="n">
-        <v>7.82819747924805</v>
+        <v>7.82819700241089</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G79" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H79" t="n">
         <v>400</v>
@@ -2689,7 +2689,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G80" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G81" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G82" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G83" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G84" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G85" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87370920181274</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82819747924805</v>
+        <v>7.82819700241089</v>
       </c>
       <c r="H88" t="n">
         <v>600</v>
@@ -3037,7 +3037,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3066,7 +3066,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -21980,6 +21980,35 @@
         <v>1200</v>
       </c>
       <c r="I745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B746" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C746" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D746" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E746" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F746" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G746" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H746" t="n">
+        <v>400</v>
+      </c>
+      <c r="I746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.73717164993286</v>
+        <v>7.73717212677002</v>
       </c>
       <c r="H2" t="n">
         <v>18200</v>
@@ -456,7 +456,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>7.69620943069458</v>
+        <v>7.69621086120605</v>
       </c>
       <c r="H3" t="n">
         <v>3600</v>
@@ -543,7 +543,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91922235488892</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H6" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91011953353882</v>
+        <v>7.91012001037598</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>7.91011953353882</v>
+        <v>7.91012001037598</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G9" t="n">
-        <v>7.88281202316284</v>
+        <v>7.88281297683716</v>
       </c>
       <c r="H9" t="n">
         <v>5800</v>
@@ -659,7 +659,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640169143677</v>
+        <v>7.84640216827393</v>
       </c>
       <c r="H10" t="n">
         <v>5000</v>
@@ -688,7 +688,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G11" t="n">
-        <v>7.90101766586304</v>
+        <v>7.90101718902588</v>
       </c>
       <c r="H11" t="n">
         <v>3600</v>
@@ -746,7 +746,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G13" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H13" t="n">
         <v>200</v>
@@ -775,7 +775,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G14" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H14" t="n">
         <v>1400</v>
@@ -804,7 +804,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G15" t="n">
-        <v>7.7553768157959</v>
+        <v>7.75537729263306</v>
       </c>
       <c r="H15" t="n">
         <v>1000</v>
@@ -833,7 +833,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G16" t="n">
-        <v>7.7553768157959</v>
+        <v>7.75537729263306</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H18" t="n">
         <v>1600</v>
@@ -920,7 +920,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>7.66435050964355</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -978,7 +978,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>7.66435050964355</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H25" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G26" t="n">
-        <v>7.60973596572876</v>
+        <v>7.6097354888916</v>
       </c>
       <c r="H26" t="n">
         <v>1600</v>
@@ -1181,7 +1181,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H28" t="n">
         <v>1600</v>
@@ -1355,7 +1355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H34" t="n">
         <v>1200</v>
@@ -1384,7 +1384,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H36" t="n">
         <v>1200</v>
@@ -1442,7 +1442,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H38" t="n">
         <v>15400</v>
@@ -1529,7 +1529,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H40" t="n">
         <v>3400</v>
@@ -1558,7 +1558,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H43" t="n">
         <v>400</v>
@@ -1645,7 +1645,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H44" t="n">
         <v>200</v>
@@ -1674,7 +1674,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>8.25</v>
       </c>
       <c r="G50" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H50" t="n">
         <v>200</v>
@@ -1848,7 +1848,7 @@
         <v>8.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H51" t="n">
         <v>3000</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H52" t="n">
         <v>800</v>
@@ -1906,7 +1906,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H54" t="n">
         <v>1800</v>
@@ -1964,7 +1964,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.78268384933472</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H69" t="n">
         <v>800</v>
@@ -2399,7 +2399,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H71" t="n">
         <v>600</v>
@@ -2457,7 +2457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>7.91922235488892</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G77" t="n">
-        <v>7.82819700241089</v>
+        <v>7.82819747924805</v>
       </c>
       <c r="H77" t="n">
         <v>400</v>
@@ -2631,7 +2631,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G78" t="n">
-        <v>7.82819700241089</v>
+        <v>7.82819747924805</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82819700241089</v>
+        <v>7.82819747924805</v>
       </c>
       <c r="H88" t="n">
         <v>600</v>
@@ -2950,7 +2950,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H89" t="n">
         <v>3200</v>
@@ -2979,7 +2979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H90" t="n">
         <v>800</v>
@@ -3008,7 +3008,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G91" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3066,7 +3066,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>8.25</v>
       </c>
       <c r="G97" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H97" t="n">
         <v>400</v>
@@ -3211,7 +3211,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G98" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H98" t="n">
         <v>200</v>
@@ -3472,7 +3472,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H107" t="n">
         <v>200</v>
@@ -3501,7 +3501,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -3675,7 +3675,7 @@
         <v>8.25</v>
       </c>
       <c r="G114" t="n">
-        <v>7.50960779190063</v>
+        <v>7.50960731506348</v>
       </c>
       <c r="H114" t="n">
         <v>1600</v>
@@ -3820,7 +3820,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H119" t="n">
         <v>7800</v>
@@ -3849,7 +3849,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>7.23653078079224</v>
+        <v>7.23653125762939</v>
       </c>
       <c r="H120" t="n">
         <v>400</v>
@@ -3965,7 +3965,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H124" t="n">
         <v>400</v>
@@ -3994,7 +3994,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H125" t="n">
         <v>400</v>
@@ -4023,7 +4023,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G128" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>7.5</v>
       </c>
       <c r="G140" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H140" t="n">
         <v>9600</v>
@@ -4864,7 +4864,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H155" t="n">
         <v>8000</v>
@@ -5183,7 +5183,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>6.84738731384277</v>
+        <v>6.84738779067993</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5328,7 +5328,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>6.84738731384277</v>
+        <v>6.84738779067993</v>
       </c>
       <c r="H171" t="n">
         <v>11400</v>
@@ -5502,7 +5502,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H177" t="n">
         <v>6200</v>
@@ -5531,7 +5531,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H178" t="n">
         <v>1400</v>
@@ -5676,7 +5676,7 @@
         <v>8.25</v>
       </c>
       <c r="G183" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>8.25</v>
       </c>
       <c r="G184" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G187" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H187" t="n">
         <v>800</v>
@@ -5937,7 +5937,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>8.25</v>
       </c>
       <c r="G194" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H194" t="n">
         <v>5200</v>
@@ -6140,7 +6140,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6198,7 +6198,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H201" t="n">
         <v>400</v>
@@ -6256,7 +6256,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>7.96532821655273</v>
+        <v>7.96532869338989</v>
       </c>
       <c r="H203" t="n">
         <v>1800</v>
@@ -6517,7 +6517,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G212" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H212" t="n">
         <v>400</v>
@@ -6546,7 +6546,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G215" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G223" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H223" t="n">
         <v>200</v>
@@ -6865,7 +6865,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G224" t="n">
-        <v>7.96532821655273</v>
+        <v>7.96532869338989</v>
       </c>
       <c r="H224" t="n">
         <v>1400</v>
@@ -6923,7 +6923,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H226" t="n">
         <v>1800</v>
@@ -6952,7 +6952,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H227" t="n">
         <v>1400</v>
@@ -7010,7 +7010,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H229" t="n">
         <v>400</v>
@@ -7039,7 +7039,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H230" t="n">
         <v>800</v>
@@ -7068,7 +7068,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H231" t="n">
         <v>1800</v>
@@ -7097,7 +7097,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H233" t="n">
         <v>1400</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G236" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H239" t="n">
         <v>1400</v>
@@ -7329,7 +7329,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H245" t="n">
         <v>1800</v>
@@ -7503,7 +7503,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H246" t="n">
         <v>400</v>
@@ -7532,7 +7532,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G247" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>8.25</v>
       </c>
       <c r="G249" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H249" t="n">
         <v>2800</v>
@@ -7619,7 +7619,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G250" t="n">
-        <v>8.24481391906738</v>
+        <v>8.2448148727417</v>
       </c>
       <c r="H250" t="n">
         <v>4000</v>
@@ -7648,7 +7648,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="n">
-        <v>8.38455581665039</v>
+        <v>8.38455677032471</v>
       </c>
       <c r="H251" t="n">
         <v>4400</v>
@@ -8460,7 +8460,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H279" t="n">
         <v>400</v>
@@ -8489,7 +8489,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G281" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G282" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G283" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G284" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G285" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G287" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G288" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G290" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G291" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G292" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G293" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G294" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G295" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G297" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G298" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H298" t="n">
         <v>1000</v>
@@ -9040,7 +9040,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G302" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H302" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G303" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H307" t="n">
         <v>400</v>
@@ -9301,7 +9301,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G309" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H310" t="n">
         <v>1200</v>
@@ -9388,7 +9388,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G311" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H333" t="n">
         <v>400</v>
@@ -11012,7 +11012,7 @@
         <v>7.5</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H367" t="n">
         <v>200</v>
@@ -11273,7 +11273,7 @@
         <v>7</v>
       </c>
       <c r="G376" t="n">
-        <v>6.52132177352905</v>
+        <v>6.52132129669189</v>
       </c>
       <c r="H376" t="n">
         <v>600</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="G380" t="n">
-        <v>6.52132177352905</v>
+        <v>6.52132129669189</v>
       </c>
       <c r="H380" t="n">
         <v>400</v>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.73717212677002</v>
+        <v>7.73717164993286</v>
       </c>
       <c r="H2" t="n">
         <v>18200</v>
@@ -456,7 +456,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>7.69621086120605</v>
+        <v>7.69620943069458</v>
       </c>
       <c r="H3" t="n">
         <v>3600</v>
@@ -514,7 +514,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G5" t="n">
-        <v>7.86460733413696</v>
+        <v>7.86460828781128</v>
       </c>
       <c r="H5" t="n">
         <v>1000</v>
@@ -543,7 +543,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91922187805176</v>
+        <v>7.91922283172607</v>
       </c>
       <c r="H6" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91012001037598</v>
+        <v>7.91012048721313</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>7.91012001037598</v>
+        <v>7.91012048721313</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G9" t="n">
-        <v>7.88281297683716</v>
+        <v>7.88281202316284</v>
       </c>
       <c r="H9" t="n">
         <v>5800</v>
@@ -659,7 +659,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640216827393</v>
+        <v>7.84640169143677</v>
       </c>
       <c r="H10" t="n">
         <v>5000</v>
@@ -746,7 +746,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G13" t="n">
-        <v>7.79178667068481</v>
+        <v>7.79178762435913</v>
       </c>
       <c r="H13" t="n">
         <v>200</v>
@@ -775,7 +775,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G14" t="n">
-        <v>7.79178667068481</v>
+        <v>7.79178762435913</v>
       </c>
       <c r="H14" t="n">
         <v>1400</v>
@@ -891,7 +891,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H18" t="n">
         <v>1600</v>
@@ -920,7 +920,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>7.66435146331787</v>
+        <v>7.66435098648071</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -978,7 +978,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>7.66435146331787</v>
+        <v>7.66435098648071</v>
       </c>
       <c r="H25" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G26" t="n">
-        <v>7.6097354888916</v>
+        <v>7.60973596572876</v>
       </c>
       <c r="H26" t="n">
         <v>1600</v>
@@ -1181,7 +1181,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H28" t="n">
         <v>1600</v>
@@ -1355,7 +1355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H34" t="n">
         <v>1200</v>
@@ -1384,7 +1384,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H36" t="n">
         <v>1200</v>
@@ -1442,7 +1442,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H38" t="n">
         <v>15400</v>
@@ -1529,7 +1529,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H40" t="n">
         <v>3400</v>
@@ -1558,7 +1558,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H43" t="n">
         <v>400</v>
@@ -1732,7 +1732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>8.25</v>
       </c>
       <c r="G50" t="n">
-        <v>7.50960731506348</v>
+        <v>7.50960779190063</v>
       </c>
       <c r="H50" t="n">
         <v>200</v>
@@ -1848,7 +1848,7 @@
         <v>8.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.50960731506348</v>
+        <v>7.50960779190063</v>
       </c>
       <c r="H51" t="n">
         <v>3000</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H52" t="n">
         <v>800</v>
@@ -1906,7 +1906,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1993,7 +1993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H69" t="n">
         <v>800</v>
@@ -2399,7 +2399,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H71" t="n">
         <v>600</v>
@@ -2457,7 +2457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>7.91922187805176</v>
+        <v>7.91922283172607</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G79" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H79" t="n">
         <v>400</v>
@@ -2689,7 +2689,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G80" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G81" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G82" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G83" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G84" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G85" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>7.87370920181274</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H89" t="n">
         <v>3200</v>
@@ -2979,7 +2979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H90" t="n">
         <v>800</v>
@@ -3008,7 +3008,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G91" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3066,7 +3066,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>8.25</v>
       </c>
       <c r="G97" t="n">
-        <v>7.50960731506348</v>
+        <v>7.50960779190063</v>
       </c>
       <c r="H97" t="n">
         <v>400</v>
@@ -3211,7 +3211,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G98" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H98" t="n">
         <v>200</v>
@@ -3646,7 +3646,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -3675,7 +3675,7 @@
         <v>8.25</v>
       </c>
       <c r="G114" t="n">
-        <v>7.50960731506348</v>
+        <v>7.50960779190063</v>
       </c>
       <c r="H114" t="n">
         <v>1600</v>
@@ -3820,7 +3820,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H119" t="n">
         <v>7800</v>
@@ -3849,7 +3849,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>7.23653125762939</v>
+        <v>7.23653078079224</v>
       </c>
       <c r="H120" t="n">
         <v>400</v>
@@ -3965,7 +3965,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H124" t="n">
         <v>400</v>
@@ -3994,7 +3994,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H125" t="n">
         <v>400</v>
@@ -4023,7 +4023,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G128" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>7.5</v>
       </c>
       <c r="G140" t="n">
-        <v>6.9871301651001</v>
+        <v>6.98713064193726</v>
       </c>
       <c r="H140" t="n">
         <v>9600</v>
@@ -4864,7 +4864,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.9871301651001</v>
+        <v>6.98713064193726</v>
       </c>
       <c r="H155" t="n">
         <v>8000</v>
@@ -5183,7 +5183,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>6.84738779067993</v>
+        <v>6.84738731384277</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5328,7 +5328,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>6.84738779067993</v>
+        <v>6.84738731384277</v>
       </c>
       <c r="H171" t="n">
         <v>11400</v>
@@ -5502,7 +5502,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H177" t="n">
         <v>6200</v>
@@ -5531,7 +5531,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H178" t="n">
         <v>1400</v>
@@ -5676,7 +5676,7 @@
         <v>8.25</v>
       </c>
       <c r="G183" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>8.25</v>
       </c>
       <c r="G184" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G187" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H187" t="n">
         <v>800</v>
@@ -5937,7 +5937,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>8.25</v>
       </c>
       <c r="G194" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H194" t="n">
         <v>5200</v>
@@ -6140,7 +6140,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6198,7 +6198,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H201" t="n">
         <v>400</v>
@@ -6256,7 +6256,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>7.96532869338989</v>
+        <v>7.96532821655273</v>
       </c>
       <c r="H203" t="n">
         <v>1800</v>
@@ -6517,7 +6517,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G212" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H212" t="n">
         <v>400</v>
@@ -6546,7 +6546,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G215" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G223" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H223" t="n">
         <v>200</v>
@@ -6865,7 +6865,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G224" t="n">
-        <v>7.96532869338989</v>
+        <v>7.96532821655273</v>
       </c>
       <c r="H224" t="n">
         <v>1400</v>
@@ -6923,7 +6923,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H226" t="n">
         <v>1800</v>
@@ -6952,7 +6952,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H227" t="n">
         <v>1400</v>
@@ -7010,7 +7010,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H229" t="n">
         <v>400</v>
@@ -7039,7 +7039,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H230" t="n">
         <v>800</v>
@@ -7068,7 +7068,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H231" t="n">
         <v>1800</v>
@@ -7097,7 +7097,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H233" t="n">
         <v>1400</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G236" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H239" t="n">
         <v>1400</v>
@@ -7329,7 +7329,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H245" t="n">
         <v>1800</v>
@@ -7503,7 +7503,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H246" t="n">
         <v>400</v>
@@ -7532,7 +7532,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G247" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>8.25</v>
       </c>
       <c r="G249" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H249" t="n">
         <v>2800</v>
@@ -7619,7 +7619,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G250" t="n">
-        <v>8.2448148727417</v>
+        <v>8.24481391906738</v>
       </c>
       <c r="H250" t="n">
         <v>4000</v>
@@ -7648,7 +7648,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="n">
-        <v>8.38455677032471</v>
+        <v>8.38455581665039</v>
       </c>
       <c r="H251" t="n">
         <v>4400</v>
@@ -8460,7 +8460,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H279" t="n">
         <v>400</v>
@@ -8489,7 +8489,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G281" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G282" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G283" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G284" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G285" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G287" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G288" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G290" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G291" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G292" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G293" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G294" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G295" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G297" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G298" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H298" t="n">
         <v>1000</v>
@@ -9040,7 +9040,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G302" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H302" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G303" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H307" t="n">
         <v>400</v>
@@ -9301,7 +9301,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G309" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H310" t="n">
         <v>1200</v>
@@ -9388,7 +9388,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G311" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H333" t="n">
         <v>400</v>
@@ -11012,7 +11012,7 @@
         <v>7.5</v>
       </c>
       <c r="G367" t="n">
-        <v>6.9871301651001</v>
+        <v>6.98713064193726</v>
       </c>
       <c r="H367" t="n">
         <v>200</v>
@@ -11273,7 +11273,7 @@
         <v>7</v>
       </c>
       <c r="G376" t="n">
-        <v>6.52132129669189</v>
+        <v>6.52132177352905</v>
       </c>
       <c r="H376" t="n">
         <v>600</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="G380" t="n">
-        <v>6.52132129669189</v>
+        <v>6.52132177352905</v>
       </c>
       <c r="H380" t="n">
         <v>400</v>
@@ -22009,6 +22009,35 @@
         <v>400</v>
       </c>
       <c r="I746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B747" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C747" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D747" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E747" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F747" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G747" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H747" t="n">
+        <v>0</v>
+      </c>
+      <c r="I747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.73717164993286</v>
+        <v>7.7371711730957</v>
       </c>
       <c r="H2" t="n">
         <v>18200</v>
@@ -456,7 +456,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>7.69620943069458</v>
+        <v>7.69620990753174</v>
       </c>
       <c r="H3" t="n">
         <v>3600</v>
@@ -514,7 +514,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G5" t="n">
-        <v>7.86460828781128</v>
+        <v>7.86460733413696</v>
       </c>
       <c r="H5" t="n">
         <v>1000</v>
@@ -543,7 +543,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91922283172607</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H6" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91012048721313</v>
+        <v>7.91012001037598</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>7.91012048721313</v>
+        <v>7.91012001037598</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640169143677</v>
+        <v>7.84640216827393</v>
       </c>
       <c r="H10" t="n">
         <v>5000</v>
@@ -746,7 +746,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G13" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H13" t="n">
         <v>200</v>
@@ -775,7 +775,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G14" t="n">
-        <v>7.79178762435913</v>
+        <v>7.79178667068481</v>
       </c>
       <c r="H14" t="n">
         <v>1400</v>
@@ -804,7 +804,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G15" t="n">
-        <v>7.75537729263306</v>
+        <v>7.7553768157959</v>
       </c>
       <c r="H15" t="n">
         <v>1000</v>
@@ -833,7 +833,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G16" t="n">
-        <v>7.75537729263306</v>
+        <v>7.7553768157959</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H18" t="n">
         <v>1600</v>
@@ -920,7 +920,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>7.66435098648071</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -978,7 +978,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G23" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>7.66435098648071</v>
+        <v>7.66435146331787</v>
       </c>
       <c r="H25" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G26" t="n">
-        <v>7.60973596572876</v>
+        <v>7.6097354888916</v>
       </c>
       <c r="H26" t="n">
         <v>1600</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H27" t="n">
         <v>1800</v>
@@ -1181,7 +1181,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H28" t="n">
         <v>1600</v>
@@ -1210,7 +1210,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H29" t="n">
         <v>400</v>
@@ -1239,7 +1239,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G32" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>7.6279411315918</v>
+        <v>7.62794065475464</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H34" t="n">
         <v>1200</v>
@@ -1384,7 +1384,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H36" t="n">
         <v>1200</v>
@@ -1442,7 +1442,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H38" t="n">
         <v>15400</v>
@@ -1529,7 +1529,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H40" t="n">
         <v>3400</v>
@@ -1558,7 +1558,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H43" t="n">
         <v>400</v>
@@ -1645,7 +1645,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H44" t="n">
         <v>200</v>
@@ -1674,7 +1674,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H52" t="n">
         <v>800</v>
@@ -1906,7 +1906,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H54" t="n">
         <v>1800</v>
@@ -1964,7 +1964,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.78268432617188</v>
+        <v>7.78268480300903</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H69" t="n">
         <v>800</v>
@@ -2399,7 +2399,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H71" t="n">
         <v>600</v>
@@ -2457,7 +2457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614534378052</v>
+        <v>7.64614629745483</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>7.91922283172607</v>
+        <v>7.91922187805176</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G79" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H79" t="n">
         <v>400</v>
@@ -2689,7 +2689,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G80" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G81" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G82" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G83" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G84" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G85" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>7.8737096786499</v>
+        <v>7.87371015548706</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H89" t="n">
         <v>3200</v>
@@ -2979,7 +2979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H90" t="n">
         <v>800</v>
@@ -3008,7 +3008,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G91" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3066,7 +3066,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G98" t="n">
-        <v>7.55512046813965</v>
+        <v>7.55512094497681</v>
       </c>
       <c r="H98" t="n">
         <v>200</v>
@@ -3472,7 +3472,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H107" t="n">
         <v>200</v>
@@ -3501,7 +3501,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>7.46409511566162</v>
+        <v>7.46409463882446</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063314437866</v>
+        <v>7.60063409805298</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -3820,7 +3820,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H119" t="n">
         <v>7800</v>
@@ -3965,7 +3965,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>7.19101858139038</v>
+        <v>7.19101810455322</v>
       </c>
       <c r="H124" t="n">
         <v>400</v>
@@ -3994,7 +3994,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H125" t="n">
         <v>400</v>
@@ -4023,7 +4023,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G128" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>7.14550542831421</v>
+        <v>7.14550495147705</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>7.5</v>
       </c>
       <c r="G140" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H140" t="n">
         <v>9600</v>
@@ -4864,7 +4864,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H155" t="n">
         <v>8000</v>
@@ -5183,7 +5183,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>6.84738731384277</v>
+        <v>6.84738779067993</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5328,7 +5328,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>6.84738731384277</v>
+        <v>6.84738779067993</v>
       </c>
       <c r="H171" t="n">
         <v>11400</v>
@@ -5502,7 +5502,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H177" t="n">
         <v>6200</v>
@@ -5531,7 +5531,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H178" t="n">
         <v>1400</v>
@@ -5676,7 +5676,7 @@
         <v>8.25</v>
       </c>
       <c r="G183" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>8.25</v>
       </c>
       <c r="G184" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G187" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H187" t="n">
         <v>800</v>
@@ -5937,7 +5937,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>8.25</v>
       </c>
       <c r="G194" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H194" t="n">
         <v>5200</v>
@@ -6140,7 +6140,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6198,7 +6198,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H201" t="n">
         <v>400</v>
@@ -6256,7 +6256,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>7.96532821655273</v>
+        <v>7.96532869338989</v>
       </c>
       <c r="H203" t="n">
         <v>1800</v>
@@ -6517,7 +6517,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G212" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H212" t="n">
         <v>400</v>
@@ -6546,7 +6546,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G215" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G223" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H223" t="n">
         <v>200</v>
@@ -6865,7 +6865,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G224" t="n">
-        <v>7.96532821655273</v>
+        <v>7.96532869338989</v>
       </c>
       <c r="H224" t="n">
         <v>1400</v>
@@ -6923,7 +6923,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H226" t="n">
         <v>1800</v>
@@ -6952,7 +6952,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H227" t="n">
         <v>1400</v>
@@ -7010,7 +7010,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H229" t="n">
         <v>400</v>
@@ -7039,7 +7039,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H230" t="n">
         <v>800</v>
@@ -7068,7 +7068,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H231" t="n">
         <v>1800</v>
@@ -7097,7 +7097,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H233" t="n">
         <v>1400</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G236" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H239" t="n">
         <v>1400</v>
@@ -7329,7 +7329,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H245" t="n">
         <v>1800</v>
@@ -7503,7 +7503,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H246" t="n">
         <v>400</v>
@@ -7532,7 +7532,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G247" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>8.25</v>
       </c>
       <c r="G249" t="n">
-        <v>7.6858434677124</v>
+        <v>7.68584299087524</v>
       </c>
       <c r="H249" t="n">
         <v>2800</v>
@@ -7619,7 +7619,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G250" t="n">
-        <v>8.24481391906738</v>
+        <v>8.2448148727417</v>
       </c>
       <c r="H250" t="n">
         <v>4000</v>
@@ -7648,7 +7648,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="n">
-        <v>8.38455581665039</v>
+        <v>8.38455677032471</v>
       </c>
       <c r="H251" t="n">
         <v>4400</v>
@@ -8460,7 +8460,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H279" t="n">
         <v>400</v>
@@ -8489,7 +8489,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G281" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G282" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G283" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G284" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G285" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G287" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G288" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G290" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G291" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G292" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G293" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G294" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G295" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G297" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G298" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H298" t="n">
         <v>1000</v>
@@ -9040,7 +9040,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G302" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H302" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G303" t="n">
-        <v>7.82558536529541</v>
+        <v>7.82558584213257</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H307" t="n">
         <v>400</v>
@@ -9301,7 +9301,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G309" t="n">
-        <v>7.77900505065918</v>
+        <v>7.77900552749634</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H310" t="n">
         <v>1200</v>
@@ -9388,7 +9388,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G311" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>7.73242425918579</v>
+        <v>7.73242473602295</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>7.49952030181885</v>
+        <v>7.49951982498169</v>
       </c>
       <c r="H333" t="n">
         <v>400</v>
@@ -11012,7 +11012,7 @@
         <v>7.5</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98713064193726</v>
+        <v>6.9871301651001</v>
       </c>
       <c r="H367" t="n">
         <v>200</v>
@@ -11273,7 +11273,7 @@
         <v>7</v>
       </c>
       <c r="G376" t="n">
-        <v>6.52132177352905</v>
+        <v>6.52132129669189</v>
       </c>
       <c r="H376" t="n">
         <v>600</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="G380" t="n">
-        <v>6.52132177352905</v>
+        <v>6.52132129669189</v>
       </c>
       <c r="H380" t="n">
         <v>400</v>
@@ -22038,6 +22038,64 @@
         <v>0</v>
       </c>
       <c r="I747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B748" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C748" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D748" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E748" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F748" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G748" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B749" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C749" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D749" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E749" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F749" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G749" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H749" t="n">
+        <v>800</v>
+      </c>
+      <c r="I749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>7.69165849685669</v>
+        <v>7.69165802001953</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -572,7 +572,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91012001037598</v>
+        <v>7.91011953353882</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>7.91012001037598</v>
+        <v>7.91011953353882</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640216827393</v>
+        <v>7.84640264511108</v>
       </c>
       <c r="H10" t="n">
         <v>5000</v>
@@ -688,7 +688,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G11" t="n">
-        <v>7.90101718902588</v>
+        <v>7.9010181427002</v>
       </c>
       <c r="H11" t="n">
         <v>3600</v>
@@ -717,7 +717,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>7.80999183654785</v>
+        <v>7.80999279022217</v>
       </c>
       <c r="H12" t="n">
         <v>2600</v>
@@ -891,7 +891,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H18" t="n">
         <v>1600</v>
@@ -920,7 +920,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H28" t="n">
         <v>1600</v>
@@ -1355,7 +1355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H34" t="n">
         <v>1200</v>
@@ -1384,7 +1384,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H36" t="n">
         <v>1200</v>
@@ -1442,7 +1442,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H38" t="n">
         <v>15400</v>
@@ -1500,7 +1500,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>7.69165849685669</v>
+        <v>7.69165802001953</v>
       </c>
       <c r="H39" t="n">
         <v>7600</v>
@@ -1529,7 +1529,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H40" t="n">
         <v>3400</v>
@@ -1558,7 +1558,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H43" t="n">
         <v>400</v>
@@ -1732,7 +1732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G52" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H52" t="n">
         <v>800</v>
@@ -1906,7 +1906,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1993,7 +1993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.78268480300903</v>
+        <v>7.78268432617188</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H69" t="n">
         <v>800</v>
@@ -2399,7 +2399,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H71" t="n">
         <v>600</v>
@@ -2457,7 +2457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614629745483</v>
+        <v>7.64614582061768</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G79" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H79" t="n">
         <v>400</v>
@@ -2689,7 +2689,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G80" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G81" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G82" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G83" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G84" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G85" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>7.87371015548706</v>
+        <v>7.8737096786499</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H89" t="n">
         <v>3200</v>
@@ -2979,7 +2979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H90" t="n">
         <v>800</v>
@@ -3008,7 +3008,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G91" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3066,7 +3066,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G98" t="n">
-        <v>7.55512094497681</v>
+        <v>7.55512046813965</v>
       </c>
       <c r="H98" t="n">
         <v>200</v>
@@ -3646,7 +3646,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063409805298</v>
+        <v>7.60063362121582</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -3820,7 +3820,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H119" t="n">
         <v>7800</v>
@@ -3965,7 +3965,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>7.19101810455322</v>
+        <v>7.19101858139038</v>
       </c>
       <c r="H124" t="n">
         <v>400</v>
@@ -3994,7 +3994,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H125" t="n">
         <v>400</v>
@@ -4023,7 +4023,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G128" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>7.14550495147705</v>
+        <v>7.14550542831421</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>7.5</v>
       </c>
       <c r="G140" t="n">
-        <v>6.9871301651001</v>
+        <v>6.98713064193726</v>
       </c>
       <c r="H140" t="n">
         <v>9600</v>
@@ -4864,7 +4864,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="n">
-        <v>6.9871301651001</v>
+        <v>6.98713064193726</v>
       </c>
       <c r="H155" t="n">
         <v>8000</v>
@@ -5183,7 +5183,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>6.84738779067993</v>
+        <v>6.84738731384277</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5328,7 +5328,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>6.84738779067993</v>
+        <v>6.84738731384277</v>
       </c>
       <c r="H171" t="n">
         <v>11400</v>
@@ -5502,7 +5502,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H177" t="n">
         <v>6200</v>
@@ -5531,7 +5531,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H178" t="n">
         <v>1400</v>
@@ -5676,7 +5676,7 @@
         <v>8.25</v>
       </c>
       <c r="G183" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>8.25</v>
       </c>
       <c r="G184" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G187" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H187" t="n">
         <v>800</v>
@@ -5937,7 +5937,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>8.25</v>
       </c>
       <c r="G194" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H194" t="n">
         <v>5200</v>
@@ -6140,7 +6140,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6198,7 +6198,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H201" t="n">
         <v>400</v>
@@ -6256,7 +6256,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>7.96532869338989</v>
+        <v>7.96532821655273</v>
       </c>
       <c r="H203" t="n">
         <v>1800</v>
@@ -6517,7 +6517,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G212" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H212" t="n">
         <v>400</v>
@@ -6546,7 +6546,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G215" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G223" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H223" t="n">
         <v>200</v>
@@ -6865,7 +6865,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G224" t="n">
-        <v>7.96532869338989</v>
+        <v>7.96532821655273</v>
       </c>
       <c r="H224" t="n">
         <v>1400</v>
@@ -6923,7 +6923,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H226" t="n">
         <v>1800</v>
@@ -6952,7 +6952,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H227" t="n">
         <v>1400</v>
@@ -7010,7 +7010,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H229" t="n">
         <v>400</v>
@@ -7039,7 +7039,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H230" t="n">
         <v>800</v>
@@ -7068,7 +7068,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H231" t="n">
         <v>1800</v>
@@ -7097,7 +7097,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H233" t="n">
         <v>1400</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G236" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H239" t="n">
         <v>1400</v>
@@ -7329,7 +7329,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G240" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H245" t="n">
         <v>1800</v>
@@ -7503,7 +7503,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H246" t="n">
         <v>400</v>
@@ -7532,7 +7532,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G247" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>8.25</v>
       </c>
       <c r="G249" t="n">
-        <v>7.68584299087524</v>
+        <v>7.6858434677124</v>
       </c>
       <c r="H249" t="n">
         <v>2800</v>
@@ -7619,7 +7619,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G250" t="n">
-        <v>8.2448148727417</v>
+        <v>8.24481391906738</v>
       </c>
       <c r="H250" t="n">
         <v>4000</v>
@@ -7648,7 +7648,7 @@
         <v>9</v>
       </c>
       <c r="G251" t="n">
-        <v>8.38455677032471</v>
+        <v>8.38455581665039</v>
       </c>
       <c r="H251" t="n">
         <v>4400</v>
@@ -8460,7 +8460,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H279" t="n">
         <v>400</v>
@@ -8489,7 +8489,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G281" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G282" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G283" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G284" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G285" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G287" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G288" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G290" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G291" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G292" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G293" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G294" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G295" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G297" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G298" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H298" t="n">
         <v>1000</v>
@@ -9040,7 +9040,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G302" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H302" t="n">
         <v>1000</v>
@@ -9156,7 +9156,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G303" t="n">
-        <v>7.82558584213257</v>
+        <v>7.82558536529541</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H307" t="n">
         <v>400</v>
@@ -9301,7 +9301,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G309" t="n">
-        <v>7.77900552749634</v>
+        <v>7.77900505065918</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H310" t="n">
         <v>1200</v>
@@ -9388,7 +9388,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G311" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>7.73242473602295</v>
+        <v>7.73242425918579</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>7.49951982498169</v>
+        <v>7.49952030181885</v>
       </c>
       <c r="H333" t="n">
         <v>400</v>
@@ -11012,7 +11012,7 @@
         <v>7.5</v>
       </c>
       <c r="G367" t="n">
-        <v>6.9871301651001</v>
+        <v>6.98713064193726</v>
       </c>
       <c r="H367" t="n">
         <v>200</v>
@@ -11273,7 +11273,7 @@
         <v>7</v>
       </c>
       <c r="G376" t="n">
-        <v>6.52132129669189</v>
+        <v>6.52132177352905</v>
       </c>
       <c r="H376" t="n">
         <v>600</v>
@@ -11389,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="G380" t="n">
-        <v>6.52132129669189</v>
+        <v>6.52132177352905</v>
       </c>
       <c r="H380" t="n">
         <v>400</v>
@@ -22096,6 +22096,35 @@
         <v>800</v>
       </c>
       <c r="I749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B750" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C750" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="D750" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="E750" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F750" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G750" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="H750" t="n">
+        <v>600</v>
+      </c>
+      <c r="I750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VARV.MI.xlsx
+++ b/data/VARV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.7371711730957</v>
+        <v>7.73717164993286</v>
       </c>
       <c r="H2" t="n">
         <v>18200</v>
@@ -456,7 +456,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>7.69620990753174</v>
+        <v>7.69620943069458</v>
       </c>
       <c r="H3" t="n">
         <v>3600</v>
@@ -485,7 +485,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>7.69165802001953</v>
+        <v>7.69165849685669</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -514,7 +514,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G5" t="n">
-        <v>7.86460733413696</v>
+        <v>7.86460828781128</v>
       </c>
       <c r="H5" t="n">
         <v>1000</v>
@@ -543,7 +543,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91922187805176</v>
+        <v>7.91922283172607</v>
       </c>
       <c r="H6" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91011953353882</v>
+        <v>7.91012048721313</v>
       </c>
       <c r="H7" t="n">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>7.91011953353882</v>
+        <v>7.91012048721313</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>7.84640264511108</v>
+        <v>7.84640169143677</v>
       </c>
       <c r="H10" t="n">
         <v>5000</v>
@@ -688,7 +688,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G11" t="n">
-        <v>7.9010181427002</v>
+        <v>7.90101718902588</v>
       </c>
       <c r="H11" t="n">
         <v>3600</v>
@@ -717,7 +717,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>7.80999279022217</v>
+        <v>7.80999183654785</v>
       </c>
       <c r="H12" t="n">
         <v>2600</v>
@@ -746,7 +746,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G13" t="n">
-        <v>7.79178667068481</v>
+        <v>7.79178762435913</v>
       </c>
       <c r="H13" t="n">
         <v>200</v>
@@ -775,7 +775,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G14" t="n">
-        <v>7.79178667068481</v>
+        <v>7.79178762435913</v>
       </c>
       <c r="H14" t="n">
         <v>1400</v>
@@ -804,7 +804,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G15" t="n">
-        <v>7.7553768157959</v>
+        <v>7.75537729263306</v>
       </c>
       <c r="H15" t="n">
         <v>1000</v>
@@ -833,7 +833,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G16" t="n">
-        <v>7.7553768157959</v>
+        <v>7.75537729263306</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G18" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H18" t="n">
         <v>1600</v>
@@ -920,7 +920,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G19" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>7.66435146331787</v>
+        <v>7.66435098648071</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -978,7 +978,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G21" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G22" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G23" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H23" t="n">
         <v>400</v>
@@ -1065,7 +1065,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>7.66435146331787</v>
+        <v>7.66435098648071</v>
       </c>
       <c r="H25" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G26" t="n">
-        <v>7.6097354888916</v>
+        <v>7.60973596572876</v>
       </c>
       <c r="H26" t="n">
         <v>1600</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H27" t="n">
         <v>1800</v>
@@ -1181,7 +1181,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G28" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H28" t="n">
         <v>1600</v>
@@ -1210,7 +1210,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G29" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H29" t="n">
         <v>400</v>
@@ -1239,7 +1239,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G32" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>7.62794065475464</v>
+        <v>7.6279411315918</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G34" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H34" t="n">
         <v>1200</v>
@@ -1384,7 +1384,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G35" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G36" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H36" t="n">
         <v>1200</v>
@@ -1442,7 +1442,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G37" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H38" t="n">
         <v>15400</v>
@@ -1500,7 +1500,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>7.69165802001953</v>
+        <v>7.69165849685669</v>
       </c>
       <c r="H39" t="n">
         <v>7600</v>
@@ -1529,7 +1529,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G40" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H40" t="n">
         <v>3400</v>
@@ -1558,7 +1558,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H44" t="n">
         <v>200</v>
@@ -1674,7 +1674,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G48" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G49" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G53" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H54" t="n">
         <v>1800</v>
@@ -1964,7 +1964,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G69" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H69" t="n">
         <v>800</v>
@@ -2399,7 +2399,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G70" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G71" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H71" t="n">
         <v>600</v>
@@ -2457,7 +2457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G72" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G73" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G75" t="n">
-        <v>7.64614582061768</v>
+        <v>7.64614534378052</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>7.91922187805176</v>
+        <v>7.91922283172607</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -3037,7 +3037,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G92" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3066,7 +3066,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G93" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G94" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H107" t="n">
         <v>200</v>
@@ -3501,7 +3501,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>7.46409463882446</v>
+        <v>7.46409511566162</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G113" t="n">
-        <v>7.60063362121582</v>
+        <v>7.60063314437866</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -22125,6 +22125,35 @@
         <v>600</v>
       </c>
       <c r="I750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B751" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C751" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="D751" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="E751" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="F751" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="G751" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="H751" t="n">
+        <v>400</v>
+      </c>
+      <c r="I751" t="s">
         <v>9</v>
       </c>
     </row>
